--- a/Donnees/Statistiques Démographiques et sociales/Emploi/Theme_Emploi.xlsx
+++ b/Donnees/Statistiques Démographiques et sociales/Emploi/Theme_Emploi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Ansade_Project\Donnees\Statistiques Démographiques et sociales\Emploi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EE6FFBB-C8DA-4CCA-8442-58716A0F6A57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{917FD328-82FF-49B9-860B-3987F2C7A482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Taux de participation" sheetId="1" r:id="rId1"/>
@@ -22,10 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="39">
-  <si>
-    <t>Tableau 1.5.1: Taux de participation au marché de travail</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="41">
   <si>
     <t>2019</t>
   </si>
@@ -117,28 +114,37 @@
     <t>Niveau d'instruction~Aucun</t>
   </si>
   <si>
-    <t>groupe age~Total</t>
-  </si>
-  <si>
-    <t>groupe age~14 - 24</t>
-  </si>
-  <si>
-    <t>groupe age~25 - 35</t>
-  </si>
-  <si>
-    <t>groupe age~36 - 64</t>
-  </si>
-  <si>
     <t>Source : ENRE-SI/2012, ENE-SI/2017 et EPCV/2019</t>
   </si>
   <si>
-    <t>Tableau 1.5.2: Ratio emploi (Proportion des personnes en emploi sur la population en âge de travailler)</t>
-  </si>
-  <si>
-    <t>Tableau 1.5.3: Taux de chômage (population en chômage)</t>
-  </si>
-  <si>
     <t>Mauritanie</t>
+  </si>
+  <si>
+    <t>Tableau 1.5.1: Taux(%) de participation au marché du travail</t>
+  </si>
+  <si>
+    <t>Tableau 1.5.3: Taux (%) de chômage (population en chômage)</t>
+  </si>
+  <si>
+    <t>Groupe âge (année) ~Total</t>
+  </si>
+  <si>
+    <t>Groupe âge (année) ~14 - 24</t>
+  </si>
+  <si>
+    <t>Groupe âge (année)~25 - 35</t>
+  </si>
+  <si>
+    <t>Groupe âge (année)~36 - 64</t>
+  </si>
+  <si>
+    <t>Groupe âge (année)~Total</t>
+  </si>
+  <si>
+    <t>Groupe âge (année)~14 - 24</t>
+  </si>
+  <si>
+    <t>Tableau 1.5.2: Ratio emploi (Proportion de personnes en emploi sur la population en âge de travailler)</t>
   </si>
 </sst>
 </file>
@@ -504,27 +510,27 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <v>45.80894540288147</v>
@@ -541,7 +547,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4">
         <v>46.153328898372187</v>
@@ -558,7 +564,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
         <v>51.628333161398558</v>
@@ -575,7 +581,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <v>48.88529331480877</v>
@@ -592,7 +598,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7">
         <v>50.176715236369994</v>
@@ -609,7 +615,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8">
         <v>41.243546728645001</v>
@@ -626,7 +632,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9">
         <v>27.765418129972051</v>
@@ -643,7 +649,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10">
         <v>40.539732206834692</v>
@@ -660,7 +666,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11">
         <v>45.038322275032613</v>
@@ -677,7 +683,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12">
         <v>27.130818262950179</v>
@@ -694,7 +700,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13">
         <v>42.613570035429319</v>
@@ -711,7 +717,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14">
         <v>51.252647951935543</v>
@@ -728,7 +734,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15">
         <v>59.499601357436497</v>
@@ -745,7 +751,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16">
         <v>49.554857548442662</v>
@@ -762,7 +768,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17">
         <v>45.80894540288147</v>
@@ -779,7 +785,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18">
         <v>47.01469783363062</v>
@@ -796,7 +802,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19">
         <v>44.304976887753192</v>
@@ -813,7 +819,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B20">
         <v>45.80894540288147</v>
@@ -830,7 +836,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21">
         <v>63.758137159204921</v>
@@ -847,7 +853,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22">
         <v>30.745309747183121</v>
@@ -864,7 +870,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23">
         <v>45.80894540288147</v>
@@ -881,7 +887,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24">
         <v>53.331188407742573</v>
@@ -898,7 +904,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B25">
         <v>47.571029536578791</v>
@@ -915,7 +921,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B26">
         <v>34.40219073945007</v>
@@ -932,7 +938,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27">
         <v>60.058444125539218</v>
@@ -949,7 +955,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B28">
         <v>59.763185788282641</v>
@@ -966,7 +972,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B29">
         <v>46.656278250393576</v>
@@ -983,7 +989,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B30">
         <v>45.80894540288147</v>
@@ -1000,7 +1006,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B31">
         <v>24.539824767738619</v>
@@ -1017,7 +1023,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B32">
         <v>52.845431055555821</v>
@@ -1034,7 +1040,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B33">
         <v>64.361880755452759</v>
@@ -1051,7 +1057,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1069,27 +1075,27 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <v>40.21185000867905</v>
@@ -1106,7 +1112,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4">
         <v>42.333372300478089</v>
@@ -1123,7 +1129,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
         <v>46.992732509243162</v>
@@ -1140,7 +1146,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <v>46.68542003177933</v>
@@ -1157,7 +1163,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7">
         <v>44.134537126550271</v>
@@ -1174,7 +1180,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8">
         <v>35.505315972549077</v>
@@ -1191,7 +1197,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9">
         <v>22.710633599874349</v>
@@ -1208,7 +1214,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10">
         <v>36.08125012823524</v>
@@ -1225,7 +1231,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11">
         <v>41.444237737619439</v>
@@ -1242,7 +1248,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12">
         <v>26.086822931628749</v>
@@ -1259,7 +1265,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13">
         <v>40.533070856149521</v>
@@ -1276,7 +1282,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14">
         <v>44.023441675299672</v>
@@ -1293,7 +1299,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15">
         <v>45.713748642866257</v>
@@ -1310,7 +1316,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16">
         <v>41.371213504297017</v>
@@ -1327,7 +1333,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17">
         <v>40.21185000867905</v>
@@ -1344,7 +1350,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18">
         <v>39.63739655228536</v>
@@ -1361,7 +1367,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19">
         <v>40.928381769088759</v>
@@ -1378,7 +1384,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B20">
         <v>40.21185000867905</v>
@@ -1395,7 +1401,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21">
         <v>57.839008125976363</v>
@@ -1412,7 +1418,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22">
         <v>25.418477074167839</v>
@@ -1429,7 +1435,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23">
         <v>40.21185000867905</v>
@@ -1446,7 +1452,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24">
         <v>50.113233115444963</v>
@@ -1463,7 +1469,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B25">
         <v>40.510879785207898</v>
@@ -1480,7 +1486,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B26">
         <v>26.803369485991439</v>
@@ -1497,7 +1503,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27">
         <v>49.128164338382433</v>
@@ -1514,7 +1520,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B28">
         <v>44.17422559450371</v>
@@ -1531,7 +1537,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B29">
         <v>43.62269142079149</v>
@@ -1548,7 +1554,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B30">
         <v>40.21185000867905</v>
@@ -1565,7 +1571,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B31">
         <v>18.32280104119884</v>
@@ -1582,7 +1588,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B32">
         <v>45.365122220506201</v>
@@ -1599,7 +1605,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B33">
         <v>61.031092740782967</v>
@@ -1616,7 +1622,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1634,27 +1640,27 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <v>12.21834588196028</v>
@@ -1671,7 +1677,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4">
         <v>8.2766653870311497</v>
@@ -1688,7 +1694,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
         <v>8.9787920087669661</v>
@@ -1705,7 +1711,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6">
         <v>4.5000717677254203</v>
@@ -1722,7 +1728,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7">
         <v>12.04179684014111</v>
@@ -1739,7 +1745,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8">
         <v>13.913039035778629</v>
@@ -1756,7 +1762,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9">
         <v>18.20532471881338</v>
@@ -1773,7 +1779,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10">
         <v>10.997808411392819</v>
@@ -1790,7 +1796,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11">
         <v>7.9800586608563142</v>
@@ -1807,7 +1813,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12">
         <v>3.848005324436186</v>
@@ -1824,7 +1830,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13">
         <v>4.8822456732685344</v>
@@ -1841,7 +1847,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14">
         <v>14.10503957457076</v>
@@ -1858,7 +1864,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15">
         <v>23.169655594418881</v>
@@ -1875,7 +1881,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16">
         <v>16.514312519505861</v>
@@ -1892,7 +1898,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17">
         <v>12.21834588196028</v>
@@ -1909,7 +1915,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18">
         <v>15.691478667907131</v>
@@ -1926,7 +1932,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19">
         <v>7.6212546667593646</v>
@@ -1943,7 +1949,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B20">
         <v>12.21834588196028</v>
@@ -1960,7 +1966,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21">
         <v>9.2837232970727275</v>
@@ -1977,7 +1983,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22">
         <v>17.325675743121931</v>
@@ -1994,7 +2000,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23">
         <v>12.21834588196028</v>
@@ -2011,7 +2017,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24">
         <v>6.0339088409106534</v>
@@ -2028,7 +2034,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B25">
         <v>14.84128012394998</v>
@@ -2045,7 +2051,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B26">
         <v>22.088189996414389</v>
@@ -2062,7 +2068,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27">
         <v>18.19940550625893</v>
@@ -2079,7 +2085,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B28">
         <v>26.084553539371971</v>
@@ -2096,7 +2102,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B29">
         <v>6.5019906073980378</v>
@@ -2113,7 +2119,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B30">
         <v>12.21834588196028</v>
@@ -2130,7 +2136,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B31">
         <v>25.334425919426259</v>
@@ -2147,7 +2153,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B32">
         <v>14.15507203865107</v>
@@ -2164,7 +2170,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B33">
         <v>5.175094288070353</v>
@@ -2181,7 +2187,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
